--- a/projekty/hovno/data/karty.xlsx
+++ b/projekty/hovno/data/karty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Documents\ProgramKeKartam\karty\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Documents\ProgramKeKartam\karty\projekty\hovno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D5DCE62-10E6-4148-ADF1-E072320F3E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D44419-7820-4BD6-83A5-F6FC5A3645A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metro2033" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="119">
   <si>
     <t>Nazev</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>akce</t>
+  </si>
+  <si>
+    <t>kopyto</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1563,7 @@
         <v>11</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J17" s="3">
         <v>12</v>
@@ -1701,7 +1704,7 @@
         <v>83</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>116</v>

--- a/projekty/hovno/data/karty.xlsx
+++ b/projekty/hovno/data/karty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Documents\ProgramKeKartam\karty\projekty\hovno\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D44419-7820-4BD6-83A5-F6FC5A3645A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761CB04C-D432-4D72-A286-1AD83E52C260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metro2033" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
   <si>
     <t>Nazev</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>kopyto</t>
+  </si>
+  <si>
+    <t>asdfasdf</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1283,9 @@
       <c r="J11" s="3">
         <v>6</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
